--- a/3. Attributor and ShapeFileCombiner/ControlFile_AttributorCombiner.xlsx
+++ b/3. Attributor and ShapeFileCombiner/ControlFile_AttributorCombiner.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHussain\Dropbox (IRENA)\01 My work folder\2. MSR\20210105 zoning codes\2. MSR_OpenRepo\3. Attributor and ShapeFileCombiner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\3. Attributor and ShapeFileCombiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E619037B-9A68-41B9-AEFC-48A299CC7140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8F600C-5831-4F8C-9BE9-F5D04DF92159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="1485" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23880" yWindow="-6870" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PathsAndNames" sheetId="10" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -43,12 +46,21 @@
   <commentList>
     <comment ref="C7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     if csp annual CF is not to be calculated from hourly profiles
 Reply:
     for csp log equation parameters and technology name conventions etc.</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -59,14 +71,96 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={78EAB35E-4C8C-483D-BF2E-8D0C987310BE}</author>
+    <author>tc={784EB750-03AA-4950-8508-A908E943EC44}</author>
+    <author>tc={2697B9E9-70FE-4E22-B4E5-0F050E254FFB}</author>
+    <author>tc={E8D8B6FC-D208-4C26-9DD3-64C488BFDF03}</author>
+    <author>tc={0C1E3E75-C2FB-4C21-991D-1F20F344A929}</author>
   </authors>
   <commentList>
     <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Capital required for deploying two substations per transmission line. Assumed specifically for an asset capacity suitable to evacuate power from a typical utility scale power plant having a nameplate capacity in the range of 2.5 - 75 MW</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="1" shapeId="0" xr:uid="{784EB750-03AA-4950-8508-A908E943EC44}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Source: https://www.sciencedirect.com/science/article/pii/S0360544222015328
+Converted to USD</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="2" shapeId="0" xr:uid="{2697B9E9-70FE-4E22-B4E5-0F050E254FFB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    IRENA Renewable Power Generation Costs 2022 Table A1.2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="3" shapeId="0" xr:uid="{E8D8B6FC-D208-4C26-9DD3-64C488BFDF03}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    From IRENA Renewable Power Generation Costs 2022</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="4" shapeId="0" xr:uid="{0C1E3E75-C2FB-4C21-991D-1F20F344A929}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    IRENA Renewable Power Generation Costs 2022 Table A1.2</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -157,12 +251,6 @@
     <t>Address to Control Inputs Profile Generator.xlsx</t>
   </si>
   <si>
-    <t>C:\Users\BHussain\Documents\Bilal\MSRHomeDirectory\MSRCreaterOutputs</t>
-  </si>
-  <si>
-    <t>C:\Users\BHussain\Documents\Bilal\Results-Prescreen</t>
-  </si>
-  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -211,13 +299,144 @@
     <t>Supply asset Capital Recovery Factor</t>
   </si>
   <si>
-    <t>C:\Users\BHussain\Documents\Bilal\ProfileGeneratorOutputs\Results_LocalTimeProfiles</t>
-  </si>
-  <si>
-    <t>C:\Users\BHussain\Dropbox (IRENA)\01 My work folder\2. MSR\20210105 zoning codes\2. MSR_OpenRepo\countrynames.csv</t>
-  </si>
-  <si>
-    <t>C:\Users\BHussain\Dropbox (IRENA)\01 My work folder\2. MSR\20210105 zoning codes\2. MSR_OpenRepo\2. Profile Generator\ControlFile_ProfileGenerator.xlsx</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\1. MSR Creator\Output</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\2. Profile Generator\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Output_Bolivia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\Results_LocalTimeProfiles</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\countrynames.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\3. Attributor and ShapeFileCombiner\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Results-Prescreen_Bolivia</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\2. Profile Generator\ControlFile_ProfileGenerator.xlsx</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -228,7 +447,7 @@
     <numFmt numFmtId="164" formatCode="0.0000000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +459,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,7 +518,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -301,9 +527,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -338,6 +561,7 @@
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Bilal Hussain" id="{EDE8A905-5964-4A16-949B-9698484D856A}" userId="S::BHussain@irena.org::ac280622-5ae8-444b-b160-cdfbb378bbe8" providerId="AD"/>
+  <person displayName="Sebastian Hendrik Sterl" id="{3FD97F18-AD78-42B1-9610-F370FDFF1406}" userId="S::Sebastian.Sterl@vub.be::9abbcd59-8436-459b-80bb-378f3df9389c" providerId="AD"/>
 </personList>
 </file>
 
@@ -618,22 +842,41 @@
   <threadedComment ref="I1" dT="2022-02-28T09:22:44.00" personId="{EDE8A905-5964-4A16-949B-9698484D856A}" id="{78EAB35E-4C8C-483D-BF2E-8D0C987310BE}">
     <text>Capital required for deploying two substations per transmission line. Assumed specifically for an asset capacity suitable to evacuate power from a typical utility scale power plant having a nameplate capacity in the range of 2.5 - 75 MW</text>
   </threadedComment>
+  <threadedComment ref="B2" dT="2023-12-21T10:28:24.29" personId="{3FD97F18-AD78-42B1-9610-F370FDFF1406}" id="{784EB750-03AA-4950-8508-A908E943EC44}">
+    <text>Source: https://www.sciencedirect.com/science/article/pii/S0360544222015328
+Converted to USD</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>74400907</xltc2:checksum>
+        <xltc2:hyperlink startIndex="8" length="67" url="https://www.sciencedirect.com/science/article/pii/S0360544222015328"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="C2" dT="2023-12-21T10:30:55.95" personId="{3FD97F18-AD78-42B1-9610-F370FDFF1406}" id="{2697B9E9-70FE-4E22-B4E5-0F050E254FFB}">
+    <text>IRENA Renewable Power Generation Costs 2022 Table A1.2</text>
+  </threadedComment>
+  <threadedComment ref="B5" dT="2023-12-21T10:29:35.38" personId="{3FD97F18-AD78-42B1-9610-F370FDFF1406}" id="{E8D8B6FC-D208-4C26-9DD3-64C488BFDF03}">
+    <text>From IRENA Renewable Power Generation Costs 2022</text>
+  </threadedComment>
+  <threadedComment ref="C5" dT="2023-12-21T10:31:46.49" personId="{3FD97F18-AD78-42B1-9610-F370FDFF1406}" id="{0C1E3E75-C2FB-4C21-991D-1F20F344A929}">
+    <text>IRENA Renewable Power Generation Costs 2022 Table A1.2</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.90625" customWidth="1"/>
-    <col min="2" max="2" width="49.54296875" customWidth="1"/>
+    <col min="1" max="1" width="45.85546875" customWidth="1"/>
+    <col min="2" max="2" width="49.5703125" customWidth="1"/>
     <col min="3" max="3" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -642,64 +885,64 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>47</v>
@@ -718,25 +961,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.90625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="49.26953125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="49.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
@@ -744,10 +987,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -755,10 +998,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -766,10 +1009,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -787,289 +1030,289 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.90625" customWidth="1"/>
-    <col min="2" max="2" width="13.26953125" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" customWidth="1"/>
-    <col min="4" max="4" width="13.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9.54296875" customWidth="1"/>
-    <col min="7" max="7" width="12.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.90625" customWidth="1"/>
-    <col min="9" max="9" width="9.90625" customWidth="1"/>
-    <col min="10" max="10" width="12.453125" customWidth="1"/>
-    <col min="11" max="11" width="12.26953125" customWidth="1"/>
-    <col min="12" max="12" width="9.26953125" customWidth="1"/>
-    <col min="13" max="13" width="8.453125" customWidth="1"/>
-    <col min="14" max="14" width="8.6328125" customWidth="1"/>
-    <col min="15" max="15" width="18.7265625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="10.6328125" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" customWidth="1"/>
+    <col min="13" max="13" width="8.42578125" customWidth="1"/>
+    <col min="14" max="14" width="8.5703125" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="8" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:16" s="7" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="J1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5">
-        <v>1337.5</v>
-      </c>
-      <c r="C2" s="5">
-        <v>64200.000000000007</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="B2" s="4">
+        <v>1177.2</v>
+      </c>
+      <c r="C2" s="4">
+        <v>31000</v>
+      </c>
+      <c r="D2" s="4">
         <v>0</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <f t="shared" ref="E2:E5" si="0">P2*(1+P2)^F2 / ((1+P2)^F2 - 1)</f>
         <v>0.11016807219002084</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <v>25</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>1059.3</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>0</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <v>75970</v>
       </c>
       <c r="J2" s="3">
         <f t="shared" ref="J2:J5" si="1">P2*(1+P2)^K2 / ((1+P2)^K2 - 1)</f>
         <v>0.10225941441436948</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <v>40</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>435490</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
         <v>0</v>
       </c>
       <c r="N2" s="3">
         <f t="shared" ref="N2:N5" si="2">P2*(1+P2)^O2 / ((1+P2)^O2 - 1)</f>
         <v>0.11016807219002084</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="4">
         <v>25</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5">
-        <v>1551.5</v>
-      </c>
-      <c r="C3" s="5">
-        <v>64200.000000000007</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="B3" s="4">
+        <v>1411.5500000000002</v>
+      </c>
+      <c r="C3" s="4">
+        <v>31000</v>
+      </c>
+      <c r="D3" s="4">
         <v>0</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <f t="shared" si="0"/>
         <v>0.11016807219002084</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>25</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>1059.3</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>0</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="4">
         <v>75970</v>
       </c>
       <c r="J3" s="3">
         <f t="shared" si="1"/>
         <v>0.10225941441436948</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="4">
         <v>40</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="4">
         <v>435490</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="4">
         <v>0</v>
       </c>
       <c r="N3" s="3">
         <f t="shared" si="2"/>
         <v>0.11016807219002084</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="4">
         <v>25</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5">
-        <v>1819</v>
-      </c>
-      <c r="C4" s="5">
-        <v>64200.000000000007</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="B4" s="4">
+        <v>1520.5500000000002</v>
+      </c>
+      <c r="C4" s="4">
+        <v>31000</v>
+      </c>
+      <c r="D4" s="4">
         <v>0</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <f t="shared" si="0"/>
         <v>0.11016807219002084</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>25</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>1059.3</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>0</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>75970</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="1"/>
         <v>0.10225941441436948</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>40</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>435490</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="4">
         <v>0</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="2"/>
         <v>0.11016807219002084</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="4">
         <v>25</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="5">
-        <v>1070</v>
-      </c>
-      <c r="C5" s="5">
-        <v>53500</v>
-      </c>
-      <c r="D5" s="5">
-        <v>4.28</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="B5" s="4">
+        <v>876</v>
+      </c>
+      <c r="C5" s="4">
+        <v>17800</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
         <f t="shared" si="0"/>
         <v>0.11016807219002084</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>25</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>1059.3</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>0</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>75970</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="1"/>
         <v>0.10225941441436948</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
         <v>40</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="4">
         <v>435490</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="4">
         <v>0</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="2"/>
         <v>0.11016807219002084</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="4">
         <v>25</v>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:16" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
